--- a/mapping/Plant.xlsx
+++ b/mapping/Plant.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3431,10 +3431,370 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
+          <t>Durio</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>榴莲属</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Suriana</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>海人树属</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Duhaldea</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>羊耳菊属</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Trivalvaria</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>三瓣木属</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Zanthoxylum</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>花椒属</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>柳属</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Typhonium</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>犁头尖属</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Casearia</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>嘉赐木属</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Cynara</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>菜蓟属</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Euchiton</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>山莴苣属</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Canna</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>美人蕉属</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Carpesium</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>天名精属</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Lycoris</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>石蒜属</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Anubias</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>水榕属</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Erigeron</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>飞蓬属</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>蝎尾蕉属</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Clematis</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>铁线莲属</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Aspidistra</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>蜘蛛抱蛋属</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Androsace</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>点地梅属</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Psydrax</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>粗叶木属</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Aglaia</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>米仔兰属</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Synostemon</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>合蕊柱属</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Bentinckia</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>本廷克椰属</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Hechtia</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>赫奇凤梨属</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Vitis</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>葡萄属</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Aleurites</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>石栗属</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Amorphophallus</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>魔芋属</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Bruguiera</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>木榄属</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Idesia</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>山桐子属</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Steudnera</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>泉七属</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
           <t>Megathyrsus</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>大黍属</t>
         </is>
